--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2024_arica_y_parinacota.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:41</t>
+    <t xml:space="preserve">2026-10-05 02:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>760712.56</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>736281.31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>743141.12</v>
+        <v>743141.13</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>802344.94</v>
@@ -822,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>825455.62</v>
+        <v>825455.63</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>876986.31</v>
@@ -836,7 +836,7 @@
         <v>753582.56</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>788099.12</v>
+        <v>788099.13</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>844828.88</v>
@@ -899,7 +899,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>782529.62</v>
+        <v>782529.63</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>852706.38</v>
@@ -913,7 +913,7 @@
         <v>773952.25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -954,7 +954,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>876672.62</v>
+        <v>876672.63</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>928044.19</v>
@@ -1001,7 +1001,7 @@
         <v>820823.31</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>813870.81</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1064,7 +1064,7 @@
         <v>36</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>829006.12</v>
+        <v>829006.13</v>
       </c>
       <c r="C35" s="2" t="n">
         <v>886398.88</v>
@@ -1075,7 +1075,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>838585.62</v>
+        <v>838585.63</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>900212.25</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>843418.62</v>
+        <v>843418.63</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>917146.44</v>
@@ -1130,7 +1130,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>859745.62</v>
+        <v>859745.63</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>928672.94</v>
@@ -1166,7 +1166,7 @@
         <v>872339.94</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1273,7 +1273,7 @@
         <v>55</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>952593.62</v>
+        <v>952593.63</v>
       </c>
       <c r="C54" s="2" t="n">
         <v>1035374.06</v>
@@ -1284,10 +1284,10 @@
         <v>56</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>967609.12</v>
+        <v>967609.13</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1295,10 +1295,10 @@
         <v>57</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>985752.62</v>
+        <v>985752.63</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1342,7 +1342,7 @@
         <v>1011701.75</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1364,7 +1364,7 @@
         <v>1063662.88</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1394,7 +1394,7 @@
         <v>66</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>1071760.62</v>
+        <v>1071760.63</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>1168289.25</v>
@@ -1419,7 +1419,7 @@
         <v>1100214.25</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1438,7 +1438,7 @@
         <v>70</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1091234.62</v>
+        <v>1091234.63</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>1186515.5</v>
@@ -1460,7 +1460,7 @@
         <v>72</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1117009.12</v>
+        <v>1117009.13</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>1202545</v>
@@ -1493,7 +1493,7 @@
         <v>75</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>1144898.12</v>
+        <v>1144898.13</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>1224566.38</v>
@@ -1515,10 +1515,10 @@
         <v>77</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>1166711.62</v>
+        <v>1166711.63</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1537,7 +1537,7 @@
         <v>79</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>1141873.62</v>
+        <v>1141873.63</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>1242222.38</v>
@@ -1551,7 +1551,7 @@
         <v>1171491.25</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1199691.88</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1570,7 +1570,7 @@
         <v>82</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>1179871.12</v>
+        <v>1179871.13</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>1271870.5</v>
@@ -1584,7 +1584,7 @@
         <v>1246250.38</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
